--- a/Python/big-pitch/output/03_model_note_xgb_interaction_detection_v3.xlsx
+++ b/Python/big-pitch/output/03_model_note_xgb_interaction_detection_v3.xlsx
@@ -501,34 +501,34 @@
         <v>28</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5233357943915766</v>
+        <v>0.5217630674733911</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>46049.99998313657</v>
+        <v>46052.29408069445</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>46050.00051392361</v>
+        <v>46052.29484627315</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0005307788541666666</v>
+        <v>0.0007655728587962963</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5957761252433638</v>
+        <v>0.988029988666161</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8927827854324062</v>
+        <v>0.7408432054798569</v>
       </c>
       <c r="H2" t="n">
-        <v>4.855912520832532e-06</v>
+        <v>0.004738897937775251</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>412</v>
+        <v>564</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8481199902343008</v>
+        <v>0.9576521658365988</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -538,37 +538,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5233391241939578</v>
+        <v>0.5217777089804244</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>46049.9943871875</v>
+        <v>46052.30309207176</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>46049.99479395834</v>
+        <v>46052.30379465278</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.0004067703935185185</v>
+        <v>0.0007025855324074074</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6836260097594444</v>
+        <v>0.9742611304071765</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8995789978700123</v>
+        <v>0.8098729101635094</v>
       </c>
       <c r="H3" t="n">
-        <v>6.039961497574257e-05</v>
+        <v>0.024159724661776</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>249</v>
+        <v>459</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6500048722499461</v>
+        <v>0.9239711098656934</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -578,37 +578,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5233468991914787</v>
+        <v>0.5217782696962792</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>46050.00106056713</v>
+        <v>46052.29033496528</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>46050.00148857639</v>
+        <v>46052.2910165625</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.0004280088310185185</v>
+        <v>0.0006816021412037037</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6520567890106693</v>
+        <v>0.9077855811740621</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9194636671142258</v>
+        <v>0.8703396507439852</v>
       </c>
       <c r="H4" t="n">
-        <v>3.69870835407893e-06</v>
+        <v>0.05366359745808709</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>541</v>
+        <v>279</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5852279669194427</v>
+        <v>0.9394355448277806</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -618,37 +618,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5233472525987517</v>
+        <v>0.5217809286535533</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>46050.00217559028</v>
+        <v>46052.30529379629</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>46050.00258462963</v>
+        <v>46052.3060081713</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.0004090424537037037</v>
+        <v>0.0007143746990740741</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6040534658498963</v>
+        <v>0.9976061155707107</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9683760919455594</v>
+        <v>0.7303601552311965</v>
       </c>
       <c r="H5" t="n">
-        <v>1.258179425318517e-05</v>
+        <v>0.02115027889701121</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>229</v>
+        <v>475</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6619862446323966</v>
+        <v>0.888673687817483</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -658,37 +658,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B6" t="n">
-        <v>0.523347758144763</v>
+        <v>0.5217860227390329</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>46050.0057097338</v>
+        <v>46052.29711053241</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>46050.00613421296</v>
+        <v>46052.29779002315</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.0004244826620370371</v>
+        <v>0.0006795019907407407</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6119002432100343</v>
+        <v>0.9652383327425097</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9085570590167661</v>
+        <v>0.7612597965280045</v>
       </c>
       <c r="H6" t="n">
-        <v>1.685685824221632e-05</v>
+        <v>0.0003887046234237243</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>147</v>
+        <v>408</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7283670711675491</v>
+        <v>0.9104825940173162</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -698,37 +698,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5233548046843619</v>
+        <v>0.5217926691204967</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>46049.98976065972</v>
+        <v>46052.29903483796</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>46049.99015046296</v>
+        <v>46052.29971357639</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.0003898054513888889</v>
+        <v>0.0006787412384259259</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6128408399598984</v>
+        <v>0.9993918741325356</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9619909219214346</v>
+        <v>0.6740821605973291</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01265870096629553</v>
+        <v>0.007401748257392407</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>160</v>
+        <v>479</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6678342236121597</v>
+        <v>0.7994796293235455</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -738,37 +738,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5233564377633975</v>
+        <v>0.5217958235215046</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>46050.00491936343</v>
+        <v>46052.29644137732</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>46050.00534122685</v>
+        <v>46052.29711052083</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.0004218569675925926</v>
+        <v>0.0006691427893518519</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5978162701339305</v>
+        <v>0.9751574253005152</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9707674822883828</v>
+        <v>0.8122719575376807</v>
       </c>
       <c r="H8" t="n">
-        <v>2.202026573540952e-06</v>
+        <v>0.03033680787342682</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>406</v>
+        <v>469</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6050618540835107</v>
+        <v>0.9226587148787183</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -778,37 +778,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B9" t="n">
-        <v>0.523360128659476</v>
+        <v>0.5217996259057637</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>46049.99834827546</v>
+        <v>46052.29971358796</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>46049.9988096875</v>
+        <v>46052.30036280092</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.0004614058217592592</v>
+        <v>0.0006492126851851852</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8106621271482123</v>
+        <v>0.9311923017541734</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8918371867942947</v>
+        <v>0.6867262054219923</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001623123675160388</v>
+        <v>0.01198097695505565</v>
       </c>
       <c r="I9" t="n">
         <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>376</v>
+        <v>206</v>
       </c>
       <c r="K9" t="n">
-        <v>0.870386926274161</v>
+        <v>0.8021907471822373</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -818,37 +818,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B10" t="n">
-        <v>0.523361279989915</v>
+        <v>0.5218011602506815</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>46050.00293671296</v>
+        <v>46052.30168855324</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>46050.00339028935</v>
+        <v>46052.30236142361</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.0004535819675925926</v>
+        <v>0.0006728721759259259</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5329477174423356</v>
+        <v>0.8942968414902877</v>
       </c>
       <c r="G10" t="n">
-        <v>0.976178988991603</v>
+        <v>0.6891894495986435</v>
       </c>
       <c r="H10" t="n">
-        <v>2.283253735811672e-05</v>
+        <v>0.0003552459736251283</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>479</v>
+        <v>279</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5946277266206598</v>
+        <v>0.8758107981320498</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -858,37 +858,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5233646060181025</v>
+        <v>0.5218023155008424</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>46050.00818944444</v>
+        <v>46052.27824193287</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>46050.00861304398</v>
+        <v>46052.2789271875</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.0004235989467592592</v>
+        <v>0.000685263275462963</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7057077948916439</v>
+        <v>0.8006591385428447</v>
       </c>
       <c r="G11" t="n">
-        <v>0.999973843268513</v>
+        <v>0.7990863390699525</v>
       </c>
       <c r="H11" t="n">
-        <v>0.000190412341314392</v>
+        <v>0.001074952157404828</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8187152107381719</v>
+        <v>0.9671453176972686</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -898,37 +898,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>0.523364988911027</v>
+        <v>0.5218060304141811</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>46049.99151269676</v>
+        <v>46052.28909482639</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>46049.99195226852</v>
+        <v>46052.28975935185</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.000439565636574074</v>
+        <v>0.0006645182870370371</v>
       </c>
       <c r="F12" t="n">
-        <v>0.812458760659781</v>
+        <v>0.9911200475858406</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8409212653112859</v>
+        <v>0.8547167585886166</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0008737312959358094</v>
+        <v>0.05488883113825946</v>
       </c>
       <c r="I12" t="n">
         <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7865515104794591</v>
+        <v>0.9348952594555011</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -941,34 +941,34 @@
         <v>45</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5233653766171091</v>
+        <v>0.5218061968320404</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>46050.00691282407</v>
+        <v>46052.3060081713</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>46050.00732263889</v>
+        <v>46052.30663942129</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.0004098112037037037</v>
+        <v>0.0006312493518518519</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5988887997882586</v>
+        <v>0.9560856439802604</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9143024026518137</v>
+        <v>0.7313295273477936</v>
       </c>
       <c r="H13" t="n">
-        <v>4.441292400680265e-06</v>
+        <v>0.01809869847872205</v>
       </c>
       <c r="I13" t="n">
         <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7593352804055531</v>
+        <v>0.8995683122839064</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -978,37 +978,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5233664123353459</v>
+        <v>0.5218077858139808</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>46049.99685475694</v>
+        <v>46052.29101657408</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>46049.99729498842</v>
+        <v>46052.29165434028</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.0004402360763888889</v>
+        <v>0.0006377657407407408</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8137332169184496</v>
+        <v>0.9191175594478779</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8391262256903871</v>
+        <v>0.8629165604956325</v>
       </c>
       <c r="H14" t="n">
-        <v>0.000916561924105966</v>
+        <v>0.02843052679483453</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7874913448714164</v>
+        <v>0.9424048142670677</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1018,37 +1018,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5233715792453261</v>
+        <v>0.5218078185797524</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>46050.00377434028</v>
+        <v>46052.30457018519</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>46050.00415026621</v>
+        <v>46052.30529378472</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.0003759192824074074</v>
+        <v>0.0007235953935185185</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6069902174531301</v>
+        <v>0.9343964962973308</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9475929255246897</v>
+        <v>0.7035433032596216</v>
       </c>
       <c r="H15" t="n">
-        <v>5.340954274156554e-06</v>
+        <v>0.002827597854487416</v>
       </c>
       <c r="I15" t="n">
         <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>257</v>
+        <v>199</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7138349419697879</v>
+        <v>0.9833807379234946</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1058,37 +1058,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B16" t="n">
-        <v>0.523374010438749</v>
+        <v>0.5218087126279166</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>46049.99951129629</v>
+        <v>46052.28514100694</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>46049.99998313657</v>
+        <v>46052.28581571759</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.0004718323842592592</v>
+        <v>0.0006747154398148149</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7290183397623052</v>
+        <v>0.8612987615562508</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9547926942929272</v>
+        <v>0.9164290620623823</v>
       </c>
       <c r="H16" t="n">
-        <v>1.370318867904092e-05</v>
+        <v>0.1495165544973579</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>978</v>
+        <v>195</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8978313146466074</v>
+        <v>0.9274915566056072</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1098,37 +1098,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B17" t="n">
-        <v>0.5233742308058967</v>
+        <v>0.5218093865713801</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>46050.0041503125</v>
+        <v>46052.30862040509</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>46050.00451571759</v>
+        <v>46052.30939314815</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.0003654019328703704</v>
+        <v>0.0007727339699074074</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6708610705605647</v>
+        <v>0.5542988570882174</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8225987406235482</v>
+        <v>0.8874008594316017</v>
       </c>
       <c r="H17" t="n">
-        <v>3.468674719586415e-05</v>
+        <v>0.09944807483919607</v>
       </c>
       <c r="I17" t="n">
         <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>115</v>
+        <v>248</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6510699612253271</v>
+        <v>0.8517873344575452</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1138,37 +1138,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5233751033592988</v>
+        <v>0.5218138255543077</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>46050.00534122685</v>
+        <v>46052.28975935185</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>46050.00570972222</v>
+        <v>46052.2903349537</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.0003684930787037037</v>
+        <v>0.0005755960416666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.635379919614205</v>
+        <v>0.9933596469689429</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9568458849554456</v>
+        <v>0.8344886237577736</v>
       </c>
       <c r="H18" t="n">
-        <v>6.00584869355534e-06</v>
+        <v>0.000623210592599581</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>198</v>
+        <v>56</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6678500939570902</v>
+        <v>0.8440707037425368</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1178,28 +1178,28 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5233753837960825</v>
+        <v>0.521814390292341</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>46049.99231920139</v>
+        <v>46052.283894375</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>46049.99268542824</v>
+        <v>46052.28453164352</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.0003662316666666667</v>
+        <v>0.0006372752546296296</v>
       </c>
       <c r="F19" t="n">
-        <v>0.655007128190049</v>
+        <v>0.8757606865238299</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9020799187062916</v>
+        <v>0.9809035869575056</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2782126225712072</v>
+        <v>0.003460110971128931</v>
       </c>
       <c r="I19" t="n">
         <v>2</v>
@@ -1208,7 +1208,7 @@
         <v>121</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5278853758204078</v>
+        <v>0.9702800193922332</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1218,37 +1218,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="B20" t="n">
-        <v>0.523375567658201</v>
+        <v>0.5218149805655476</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>46049.99612479167</v>
+        <v>46052.30379466435</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>46049.99649195602</v>
+        <v>46052.30457017361</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.0003671622106481482</v>
+        <v>0.0007755129861111112</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6829390548769206</v>
+        <v>0.9705617703785266</v>
       </c>
       <c r="G20" t="n">
-        <v>0.999576456850011</v>
+        <v>0.7563329542117924</v>
       </c>
       <c r="H20" t="n">
-        <v>0.002606350060305574</v>
+        <v>0.009991123995985009</v>
       </c>
       <c r="I20" t="n">
         <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>301</v>
+        <v>884</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6784363994879145</v>
+        <v>0.9587407367374674</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1258,37 +1258,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>0.523376545936267</v>
+        <v>0.5218197288986147</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>46049.997295</v>
+        <v>46052.29284724537</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>46049.9976625</v>
+        <v>46052.29349016204</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.0003675051851851852</v>
+        <v>0.0006429195833333333</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7775054503229148</v>
+        <v>0.8195500544891801</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8579055900226343</v>
+        <v>0.8205573828411855</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0003719463634636012</v>
+        <v>0.02386408782674527</v>
       </c>
       <c r="I21" t="n">
         <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>11</v>
+        <v>257</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6434949121463942</v>
+        <v>0.9455308907358494</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1298,37 +1298,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B22" t="n">
-        <v>0.5233773623551914</v>
+        <v>0.5218214716828017</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>46049.99797643519</v>
+        <v>46052.2845316551</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>46049.99834826389</v>
+        <v>46052.28514099537</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.0003718299189814815</v>
+        <v>0.0006093390277777778</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6314690182060627</v>
+        <v>0.8580051402888705</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9281671854110028</v>
+        <v>0.8904153146535987</v>
       </c>
       <c r="H22" t="n">
-        <v>0.001623495335516851</v>
+        <v>0.006192487532616074</v>
       </c>
       <c r="I22" t="n">
         <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="K22" t="n">
-        <v>0.704983395241667</v>
+        <v>0.9697122080138758</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1338,37 +1338,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="B23" t="n">
-        <v>0.5233781254761339</v>
+        <v>0.5218220509286378</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>46049.98818673611</v>
+        <v>46052.30663943287</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>46049.9885431713</v>
+        <v>46052.30727077546</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.0003564349074074074</v>
+        <v>0.0006313432291666667</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8455641229319888</v>
+        <v>0.7723934208738518</v>
       </c>
       <c r="G23" t="n">
-        <v>0.765798941550031</v>
+        <v>0.7737421252443596</v>
       </c>
       <c r="H23" t="n">
-        <v>4.124213095067492e-06</v>
+        <v>2.794746388491205e-05</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5830475855143961</v>
+        <v>0.8888598705489528</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1378,37 +1378,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B24" t="n">
-        <v>0.5233794013755423</v>
+        <v>0.5218245124910137</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>46049.99649195602</v>
+        <v>46052.29779003473</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>46049.99685474537</v>
+        <v>46052.29844833333</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.0003627850578703704</v>
+        <v>0.0006583014120370371</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5734478940675292</v>
+        <v>0.9586436583028994</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9212209511264914</v>
+        <v>0.7366723686329181</v>
       </c>
       <c r="H24" t="n">
-        <v>2.62288414688788e-05</v>
+        <v>0.0003739143179427847</v>
       </c>
       <c r="I24" t="n">
         <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>97</v>
+        <v>662</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5737057463697711</v>
+        <v>0.9123207032461526</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1418,37 +1418,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="B25" t="n">
-        <v>0.5233811004150409</v>
+        <v>0.5218255517491086</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>46050.00339030092</v>
+        <v>46052.27892719908</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>46050.00377434028</v>
+        <v>46052.27947258102</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.0003840339814814814</v>
+        <v>0.0005453856481481481</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6476491023888661</v>
+        <v>0.7134748438459986</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8866483040825289</v>
+        <v>0.9950367545830106</v>
       </c>
       <c r="H25" t="n">
-        <v>1.538786315661181e-06</v>
+        <v>0.0005798287364073807</v>
       </c>
       <c r="I25" t="n">
         <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>706</v>
+        <v>158</v>
       </c>
       <c r="K25" t="n">
-        <v>0.670275905625034</v>
+        <v>0.8290033660459908</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1458,37 +1458,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="B26" t="n">
-        <v>0.5233815419090434</v>
+        <v>0.5218282106115616</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>46049.98887390046</v>
+        <v>46052.29844834491</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>46049.9892419676</v>
+        <v>46052.29903482639</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.0003680729282407408</v>
+        <v>0.0005864834953703703</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9020241891784213</v>
+        <v>0.902693006522975</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9606674010023544</v>
+        <v>0.7549724392570567</v>
       </c>
       <c r="H26" t="n">
-        <v>0.004727416685316455</v>
+        <v>0.002073457558068545</v>
       </c>
       <c r="I26" t="n">
         <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>452</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7415636311691565</v>
+        <v>0.8577182714118197</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1498,37 +1498,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.5233843834597449</v>
+        <v>0.5218290792217843</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>46049.98854318287</v>
+        <v>46052.29227322917</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>46049.98887388889</v>
+        <v>46052.2928472338</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.0003307030671296297</v>
+        <v>0.0005740079513888889</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9060609428274695</v>
+        <v>0.8869443142219485</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8068576528040694</v>
+        <v>0.9445574795028227</v>
       </c>
       <c r="H27" t="n">
-        <v>1.123174034594087e-06</v>
+        <v>0.06014481005629807</v>
       </c>
       <c r="I27" t="n">
         <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>179</v>
+        <v>25</v>
       </c>
       <c r="K27" t="n">
-        <v>0.677696882867435</v>
+        <v>0.8745121901295738</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1538,37 +1538,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n">
-        <v>0.5233861946546059</v>
+        <v>0.5218360570972029</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>46050.0025846412</v>
+        <v>46052.29560778935</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>46050.00293670139</v>
+        <v>46052.29644136574</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.0003520550462962963</v>
+        <v>0.0008335746412037036</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7096673300979531</v>
+        <v>0.6630372641176105</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8017812910704381</v>
+        <v>0.7174986671394382</v>
       </c>
       <c r="H28" t="n">
-        <v>7.177375223042852e-06</v>
+        <v>0.004376244533980977</v>
       </c>
       <c r="I28" t="n">
         <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>258</v>
+        <v>676</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6235564447530056</v>
+        <v>0.9617327139619404</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1578,37 +1578,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.5233875892025001</v>
+        <v>0.5218394575219001</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>46049.99067701389</v>
+        <v>46052.29349017361</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>46049.99104440972</v>
+        <v>46052.29408069445</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.0003673947453703704</v>
+        <v>0.000590519525462963</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7720803385423416</v>
+        <v>0.9438490021155118</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9663569795155</v>
+        <v>0.8689432506897701</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0004912125974218245</v>
+        <v>0.1972690417767676</v>
       </c>
       <c r="I29" t="n">
         <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="K29" t="n">
-        <v>0.7372306203201987</v>
+        <v>0.8738407086410238</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1618,37 +1618,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="B30" t="n">
-        <v>0.523390178795841</v>
+        <v>0.5218495422153046</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>46050.00861304398</v>
+        <v>46052.29172631945</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>46050.00917646991</v>
+        <v>46052.29227321759</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.0005634209606481482</v>
+        <v>0.0005468990162037036</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9239353846833298</v>
+        <v>0.9230205710373284</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9438743102632003</v>
+        <v>0.7514435242322495</v>
       </c>
       <c r="H30" t="n">
-        <v>2.219470344324302e-06</v>
+        <v>0.001767517426257633</v>
       </c>
       <c r="I30" t="n">
         <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>746</v>
+        <v>362</v>
       </c>
       <c r="K30" t="n">
-        <v>0.9565297397602079</v>
+        <v>0.7962109825651373</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1658,37 +1658,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="B31" t="n">
-        <v>0.5233907012339165</v>
+        <v>0.52185411690187</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>46050.00051392361</v>
+        <v>46052.30727078704</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>46050.00106055556</v>
+        <v>46052.30804537037</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.0005466245138888889</v>
+        <v>0.000774585798611111</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5961513997210988</v>
+        <v>0.9737601665726169</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7548864454573712</v>
+        <v>0.791561052099677</v>
       </c>
       <c r="H31" t="n">
-        <v>2.986073462900349e-06</v>
+        <v>0.1186654879399005</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9386658548688243</v>
+        <v>0.9481904976624411</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -1698,37 +1698,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="B32" t="n">
-        <v>0.5233930905763522</v>
+        <v>0.5218617005268923</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>46050.00613422454</v>
+        <v>46052.28712744213</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>46050.00654450231</v>
+        <v>46052.28796966435</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0.0004102764351851852</v>
+        <v>0.0008422218171296297</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5558800297552202</v>
+        <v>0.9100993220821891</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9032866326638174</v>
+        <v>0.650624501287933</v>
       </c>
       <c r="H32" t="n">
-        <v>1.670439465756364e-05</v>
+        <v>0.06644968859961414</v>
       </c>
       <c r="I32" t="n">
         <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="K32" t="n">
-        <v>0.7591208218707185</v>
+        <v>0.9070297319856988</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -1738,37 +1738,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B33" t="n">
-        <v>0.523394192758141</v>
+        <v>0.5218771904101005</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>46049.99350116898</v>
+        <v>46052.28088577546</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>46049.99392766204</v>
+        <v>46052.28146065972</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.0004264903356481481</v>
+        <v>0.0005748909606481482</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9856186059810822</v>
+        <v>0.7903307902033583</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6762315522201162</v>
+        <v>0.8208950995526447</v>
       </c>
       <c r="H33" t="n">
-        <v>0.05821984000840853</v>
+        <v>5.527673564096294e-06</v>
       </c>
       <c r="I33" t="n">
         <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>0.839124475844248</v>
+        <v>0.6114538945354608</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -1778,37 +1778,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B34" t="n">
-        <v>0.5233945417237786</v>
+        <v>0.5218802265595317</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>46049.9988096875</v>
+        <v>46052.28269303241</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>46049.99951129629</v>
+        <v>46052.28319344908</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.0007015984837962962</v>
+        <v>0.0005004188310185185</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6610998281710246</v>
+        <v>0.7614442133134555</v>
       </c>
       <c r="G34" t="n">
-        <v>0.7325783898979479</v>
+        <v>0.9758235341740962</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0001587825363771781</v>
+        <v>0.01389538774193144</v>
       </c>
       <c r="I34" t="n">
         <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>383</v>
+        <v>624</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9878991040814606</v>
+        <v>0.6689416544705935</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -1818,37 +1818,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="B35" t="n">
-        <v>0.5233967869022685</v>
+        <v>0.5218805661698834</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>46050.00782048611</v>
+        <v>46052.2884071875</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>46050.00818943287</v>
+        <v>46052.28909481481</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0.0003689469097222222</v>
+        <v>0.0006876351041666666</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7650267690703496</v>
+        <v>0.6557077821820855</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7789009210630015</v>
+        <v>0.7880135674559801</v>
       </c>
       <c r="H35" t="n">
-        <v>1.043933568036232e-06</v>
+        <v>0.001423623448984785</v>
       </c>
       <c r="I35" t="n">
         <v>2</v>
       </c>
       <c r="J35" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6951027432055972</v>
+        <v>0.7546974133545002</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -1861,34 +1861,34 @@
         <v>14</v>
       </c>
       <c r="B36" t="n">
-        <v>0.5233995372850173</v>
+        <v>0.5218894044995895</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>46049.99392767361</v>
+        <v>46052.28581572917</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>46049.99438717592</v>
+        <v>46052.28663702546</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.0004595043518518518</v>
+        <v>0.0008212924652777778</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7367026667308819</v>
+        <v>0.8297851574441182</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9880028904410775</v>
+        <v>0.7835185198250264</v>
       </c>
       <c r="H36" t="n">
-        <v>0.02149454118089178</v>
+        <v>0.2643619924789058</v>
       </c>
       <c r="I36" t="n">
         <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>7</v>
+        <v>291</v>
       </c>
       <c r="K36" t="n">
-        <v>0.9111767863636164</v>
+        <v>0.9029214930152754</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -1898,37 +1898,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B37" t="n">
-        <v>0.5233997395936495</v>
+        <v>0.5218915597159358</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>46049.99309409722</v>
+        <v>46052.28663702546</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>46049.99350115741</v>
+        <v>46052.28712744213</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.0004070646064814815</v>
+        <v>0.0004904070138888889</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5040458159611222</v>
+        <v>0.605823674981362</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8676099039501495</v>
+        <v>0.9053434668397299</v>
       </c>
       <c r="H37" t="n">
-        <v>8.733935544644724e-05</v>
+        <v>1.144683363560707e-06</v>
       </c>
       <c r="I37" t="n">
         <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>603</v>
+        <v>10</v>
       </c>
       <c r="K37" t="n">
-        <v>0.6220194378760364</v>
+        <v>0.7664763184385768</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -1938,37 +1938,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B38" t="n">
-        <v>0.5234013837798543</v>
+        <v>0.5219084509169634</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>46050.00148857639</v>
+        <v>46052.28319346065</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>46050.00186971065</v>
+        <v>46052.28385864583</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.0003811338310185185</v>
+        <v>0.0006651867592592592</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5570090427422842</v>
+        <v>0.7381735918636688</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9098384618503574</v>
+        <v>0.6714801940137189</v>
       </c>
       <c r="H38" t="n">
-        <v>3.044083647398008e-06</v>
+        <v>4.781798743420834e-05</v>
       </c>
       <c r="I38" t="n">
         <v>2</v>
       </c>
       <c r="J38" t="n">
-        <v>575</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5742356568007753</v>
+        <v>0.8420957660586726</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -1978,37 +1978,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B39" t="n">
-        <v>0.5234108342946142</v>
+        <v>0.5219143303711882</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>46049.99268543981</v>
+        <v>46052.28146067129</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>46049.99309408565</v>
+        <v>46052.28210159722</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0.0004086479398148148</v>
+        <v>0.0006409253587962963</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7247072291449934</v>
+        <v>0.7048829642363457</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8783982594099708</v>
+        <v>0.7179979466813797</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1484708005584103</v>
+        <v>0.000159585519881693</v>
       </c>
       <c r="I39" t="n">
         <v>2</v>
       </c>
       <c r="J39" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>0.8804596030269594</v>
+        <v>0.8895525943066782</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2018,37 +2018,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B40" t="n">
-        <v>0.5234192622596664</v>
+        <v>0.52191823359959</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>46050.00451571759</v>
+        <v>46052.28796967593</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>46050.00491935185</v>
+        <v>46052.28840717593</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.0004036327199074074</v>
+        <v>0.0004374982523148149</v>
       </c>
       <c r="F40" t="n">
-        <v>0.537284146951158</v>
+        <v>0.7968392357900305</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8519070436210462</v>
+        <v>0.9232142610613518</v>
       </c>
       <c r="H40" t="n">
-        <v>9.559867579301236e-06</v>
+        <v>0.07010236138503083</v>
       </c>
       <c r="I40" t="n">
         <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>407</v>
       </c>
       <c r="K40" t="n">
-        <v>0.547834291123146</v>
+        <v>0.5260355144104041</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2058,37 +2058,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>0.5234257718523999</v>
+        <v>0.5219232671691237</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>46049.99479395834</v>
+        <v>46052.30236143518</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>46049.99528780093</v>
+        <v>46052.30309206019</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.0004938403472222222</v>
+        <v>0.0007306307523148148</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6884720947438243</v>
+        <v>0.9677899583502357</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9290063561723072</v>
+        <v>0.5452755278419125</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9480922372373276</v>
+        <v>0.00589472313905191</v>
       </c>
       <c r="I41" t="n">
         <v>2</v>
       </c>
       <c r="J41" t="n">
-        <v>240</v>
+        <v>626</v>
       </c>
       <c r="K41" t="n">
-        <v>0.6318064031868378</v>
+        <v>0.6554128933420333</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2098,37 +2098,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B42" t="n">
-        <v>0.5234337668409008</v>
+        <v>0.5219484176342351</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>46049.98924197916</v>
+        <v>46052.27755006945</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>46049.98976064815</v>
+        <v>46052.2782419213</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>0.0005186738888888889</v>
+        <v>0.0006918477777777777</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8452943849325671</v>
+        <v>0.6843880211569958</v>
       </c>
       <c r="G42" t="n">
-        <v>0.7890475297533046</v>
+        <v>0.5042396814782091</v>
       </c>
       <c r="H42" t="n">
-        <v>0.003845738289387004</v>
+        <v>0.0001273755143519654</v>
       </c>
       <c r="I42" t="n">
         <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>563</v>
+        <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>0.9799512480123098</v>
+        <v>0.8280964707788323</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2138,37 +2138,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B43" t="n">
-        <v>0.5234370247579924</v>
+        <v>0.521949368040236</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>46049.99015047454</v>
+        <v>46052.30099601852</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>46049.99067700232</v>
+        <v>46052.30168854167</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.0005265263541666667</v>
+        <v>0.0006925283217592592</v>
       </c>
       <c r="F43" t="n">
-        <v>0.530419315594189</v>
+        <v>0.9466252827087279</v>
       </c>
       <c r="G43" t="n">
-        <v>0.6406998904634665</v>
+        <v>0.5948106471197594</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0003635518527689019</v>
+        <v>0.0008376296556669569</v>
       </c>
       <c r="I43" t="n">
         <v>2</v>
       </c>
       <c r="J43" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0.80751978962024</v>
+        <v>0.8185250395166428</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2178,37 +2178,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B44" t="n">
-        <v>0.5234377593348842</v>
+        <v>0.5219576604401663</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>46050.00654451389</v>
+        <v>46052.29484628472</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>46050.0069128125</v>
+        <v>46052.29560777778</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0.0003683047916666666</v>
+        <v>0.000761502962962963</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6219462437200981</v>
+        <v>0.8412980836340701</v>
       </c>
       <c r="G44" t="n">
-        <v>0.8730368068056018</v>
+        <v>0.6293684317241576</v>
       </c>
       <c r="H44" t="n">
-        <v>4.467852954232302e-05</v>
+        <v>0.0001942438597539642</v>
       </c>
       <c r="I44" t="n">
         <v>2</v>
       </c>
       <c r="J44" t="n">
-        <v>729</v>
+        <v>982</v>
       </c>
       <c r="K44" t="n">
-        <v>0.7248522160658321</v>
+        <v>0.7967239491866115</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2218,37 +2218,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n">
-        <v>0.5234458113231744</v>
+        <v>0.521966661105324</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>46049.99195228009</v>
+        <v>46052.30804538194</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>46049.99231918981</v>
+        <v>46052.30862040509</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.0003669161689814815</v>
+        <v>0.0005750195138888889</v>
       </c>
       <c r="F45" t="n">
-        <v>0.618163341428442</v>
+        <v>0.8802562628675538</v>
       </c>
       <c r="G45" t="n">
-        <v>0.7762038060096139</v>
+        <v>0.8323208571325125</v>
       </c>
       <c r="H45" t="n">
-        <v>1.246559547754359e-05</v>
+        <v>0.03766919560639086</v>
       </c>
       <c r="I45" t="n">
         <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>21</v>
+        <v>989</v>
       </c>
       <c r="K45" t="n">
-        <v>0.6974012700068516</v>
+        <v>0.980629637806214</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2258,37 +2258,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B46" t="n">
-        <v>0.5234480804591471</v>
+        <v>0.521969181957782</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>46050.00186972223</v>
+        <v>46052.3003628125</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>46050.0021755787</v>
+        <v>46052.30099600695</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.0003058599884259259</v>
+        <v>0.0006331923842592593</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6543609585800075</v>
+        <v>0.9980556025106548</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9370190055984412</v>
+        <v>0.6087653164726698</v>
       </c>
       <c r="H46" t="n">
-        <v>1.305220554868761e-06</v>
+        <v>5.599258781080313e-05</v>
       </c>
       <c r="I46" t="n">
         <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="K46" t="n">
-        <v>0.5464331336746505</v>
+        <v>0.7190078591936142</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2298,37 +2298,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B47" t="n">
-        <v>0.5234610783210959</v>
+        <v>0.521970328951882</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>46049.99766251157</v>
+        <v>46052.27947259259</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>46049.99797642361</v>
+        <v>46052.28002649306</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.0003139174884259259</v>
+        <v>0.0005538976388888889</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6987787448905176</v>
+        <v>0.5157168482328258</v>
       </c>
       <c r="G47" t="n">
-        <v>0.8217977893301289</v>
+        <v>0.7123357496134081</v>
       </c>
       <c r="H47" t="n">
-        <v>0.02017715644637559</v>
+        <v>5.929117799347046e-05</v>
       </c>
       <c r="I47" t="n">
         <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>0.7871837877101524</v>
+        <v>0.5811925379264831</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2338,37 +2338,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="B48" t="n">
-        <v>0.5234810630425045</v>
+        <v>0.5220217636083979</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>46050.00732263889</v>
+        <v>46052.2821016088</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>46050.00782047454</v>
+        <v>46052.28269302083</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.0004978316898148149</v>
+        <v>0.0005914156481481482</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5134616192428022</v>
+        <v>0.9515104083911288</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6096230271120672</v>
+        <v>0.5594166860286126</v>
       </c>
       <c r="H48" t="n">
-        <v>1.281507133307577e-05</v>
+        <v>1.488649800689049e-05</v>
       </c>
       <c r="I48" t="n">
         <v>2</v>
       </c>
       <c r="J48" t="n">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8404624881707707</v>
+        <v>0.6877549723855942</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2378,37 +2378,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B49" t="n">
-        <v>0.5234840199841811</v>
+        <v>0.522212827190649</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>46049.99568903935</v>
+        <v>46052.28002650463</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>46049.99612478009</v>
+        <v>46052.28088576389</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>0.0004357453587962962</v>
+        <v>0.0008592618634259259</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5789694079588892</v>
+        <v>0.5298741506025164</v>
       </c>
       <c r="G49" t="n">
-        <v>0.7086277611706552</v>
+        <v>0.5111667884145589</v>
       </c>
       <c r="H49" t="n">
-        <v>6.006558387068757e-05</v>
+        <v>0.01134415996038949</v>
       </c>
       <c r="I49" t="n">
         <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>51</v>
+        <v>891</v>
       </c>
       <c r="K49" t="n">
-        <v>0.5885915480272821</v>
+        <v>0.6976177009326144</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2418,37 +2418,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B50" t="n">
-        <v>0.5235076289078109</v>
+        <v>0.5258649078337927</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>46049.99104440972</v>
+        <v>46052.29165434028</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>46049.99151269676</v>
+        <v>46052.29172630787</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.0004682780208333333</v>
+        <v>7.196148148148149e-05</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6245864854699044</v>
+        <v>0.9896726976644845</v>
       </c>
       <c r="G50" t="n">
-        <v>0.5746297454697592</v>
+        <v>0.779734292032889</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0113052849898692</v>
+        <v>0.5141762134702791</v>
       </c>
       <c r="I50" t="n">
         <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="K50" t="n">
-        <v>0.7415693690525833</v>
+        <v>0.9937821121092973</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2458,37 +2458,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B51" t="n">
-        <v>0.5235724636230906</v>
+        <v>0.5260948522893641</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>46049.9952878125</v>
+        <v>46052.28385865741</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>46049.99568902778</v>
+        <v>46052.28389436343</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.0004012134375</v>
+        <v>3.570594907407408e-05</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5706651593343812</v>
+        <v>0.9629785064427886</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5005457764915847</v>
+        <v>0.8547795312117996</v>
       </c>
       <c r="H51" t="n">
-        <v>8.330585646817689e-05</v>
+        <v>0.8080519187513185</v>
       </c>
       <c r="I51" t="n">
         <v>2</v>
       </c>
       <c r="J51" t="n">
-        <v>995</v>
+        <v>51</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5115026397694995</v>
+        <v>0.9991398504843021</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2530,79 +2530,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Duration x Face_Amount_Band_ordinal</t>
+          <t>Attained_Age x Face_Amount_Band_ordinal</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4659.414112476</v>
+        <v>11949.68721711187</v>
       </c>
       <c r="C2" t="n">
-        <v>0.169776865940123</v>
+        <v>0.2335019908024273</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Attained_Age x Smoker_Status</t>
+          <t>Duration x Face_Amount_Band_ordinal</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2755.8799306042</v>
+        <v>11053.3556764414</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1004170580744179</v>
+        <v>0.2159872897593864</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Duration x Issue_Age</t>
+          <t>Attained_Age x Duration</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2432.2365697728</v>
+        <v>7087.7144950552</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08862434032967879</v>
+        <v>0.1384969677252027</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Attained_Age x Duration</t>
+          <t>Attained_Age x Smoker_Status</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1803.4830807472</v>
+        <v>4406.4859210867</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06571420737329334</v>
+        <v>0.08610461649098236</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Attained_Age x Face_Amount_Band_ordinal</t>
+          <t>Face_Amount_Band_ordinal x Smoker_Status</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1794.670749869</v>
+        <v>4387.1523717945</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06539310908024355</v>
+        <v>0.0857268306822843</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Attained_Age x Issue_Age</t>
+          <t>Duration x Observation_Year</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1326.3743082482</v>
+        <v>2716.2558133229</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04832961133781129</v>
+        <v>0.05307679844802298</v>
       </c>
     </row>
     <row r="8">
@@ -2612,257 +2612,114 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1291.0178809216</v>
+        <v>2578.30057427878</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04704131558271258</v>
+        <v>0.05038109416947934</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Issue_Age x Observation_Year</t>
+          <t>Attained_Age x Observation_Year</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1278.1297705001</v>
+        <v>1875.5511647679</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04657170654122523</v>
+        <v>0.03664907062989747</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Issue_Age x Sex</t>
+          <t>Observation_Year x Sex</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1277.6174876988</v>
+        <v>1399.6104495277</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04655304029555995</v>
+        <v>0.02734898582488467</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Attained_Age x Issue_Year</t>
+          <t>Face_Amount_Band_ordinal x Observation_Year</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1215.9491348422</v>
+        <v>1331.4221096865</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04430600677955433</v>
+        <v>0.02601655654760348</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Issue_Age x Smoker_Status</t>
+          <t>Duration x Sex</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1209.082020897</v>
+        <v>846.8643967809001</v>
       </c>
       <c r="C12" t="n">
-        <v>0.04405578710482139</v>
+        <v>0.01654809192870488</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Observation_Year x Sex</t>
+          <t>Duration x Smoker_Status</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1201.101084547</v>
+        <v>680.2080919637</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04376498265429133</v>
+        <v>0.01329155656944736</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Attained_Age x Observation_Year</t>
+          <t>Face_Amount_Band_ordinal x Sex</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1175.346997929</v>
+        <v>678.567248353</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04282657108459486</v>
+        <v>0.01325949378464533</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Issue_Age x Issue_Year</t>
+          <t>Observation_Year x Smoker_Status</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1017.67121719988</v>
+        <v>94.9345947897</v>
       </c>
       <c r="C15" t="n">
-        <v>0.03708127795532057</v>
+        <v>0.001855062519768141</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Face_Amount_Band_ordinal x Issue_Age</t>
+          <t>Sex x Smoker_Status</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>769.9774644543</v>
+        <v>89.8442043659</v>
       </c>
       <c r="C16" t="n">
-        <v>0.02805596532180887</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Duration x Sex</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>458.4798657227</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.01670580738694738</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Duration x Observation_Year</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>421.0251753485</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.01534105641332975</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Issue_Year x Sex</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>300.833819082</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.01096159769010079</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Duration x Smoker_Status</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>244.8066205573</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.008920113086390831</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Duration x Issue_Year</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>218.3819356536</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.007957266668770856</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Issue_Year x Observation_Year</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>191.056965263</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.006961616202245249</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Face_Amount_Band_ordinal x Issue_Year</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>176.887181369</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.006445306330982535</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Observation_Year x Smoker_Status</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>142.83728506647</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.005204617149836158</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Issue_Year x Smoker_Status</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>71.60356830000001</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.002609046786280076</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Face_Amount_Band_ordinal x Smoker_Status</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>10.31544995</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.0003758680213857509</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Sex x Smoker_Status</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0.160791129</v>
-      </c>
-      <c r="C27" t="n">
-        <v>5.858808273662461e-06</v>
+        <v>0.001755594117263277</v>
       </c>
     </row>
   </sheetData>

--- a/Python/big-pitch/output/03_model_note_xgb_interaction_detection_v3.xlsx
+++ b/Python/big-pitch/output/03_model_note_xgb_interaction_detection_v3.xlsx
@@ -498,37 +498,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5217630674733911</v>
+        <v>0.521762738886147</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>46052.29408069445</v>
+        <v>46053.03246152778</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>46052.29484627315</v>
+        <v>46053.03314048611</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0007655728587962963</v>
+        <v>0.0006789635879629629</v>
       </c>
       <c r="F2" t="n">
-        <v>0.988029988666161</v>
+        <v>0.936075151753419</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7408432054798569</v>
+        <v>0.9639555748594557</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004738897937775251</v>
+        <v>1.286056107403036e-05</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>564</v>
+        <v>254</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9576521658365988</v>
+        <v>0.8381150404168652</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -538,37 +538,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5217777089804244</v>
+        <v>0.5217767174251818</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>46052.30309207176</v>
+        <v>46053.02411989583</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>46052.30379465278</v>
+        <v>46053.02475096065</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.0007025855324074074</v>
+        <v>0.0006310615046296296</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9742611304071765</v>
+        <v>0.9949690599011676</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8098729101635094</v>
+        <v>0.9947190490923821</v>
       </c>
       <c r="H3" t="n">
-        <v>0.024159724661776</v>
+        <v>0.0001667207033574375</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>459</v>
+        <v>175</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9239711098656934</v>
+        <v>0.8808360465145315</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -578,37 +578,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5217782696962792</v>
+        <v>0.5217804030263231</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>46052.29033496528</v>
+        <v>46053.03129449074</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>46052.2910165625</v>
+        <v>46053.03186405093</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.0006816021412037037</v>
+        <v>0.000569555787037037</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9077855811740621</v>
+        <v>0.9257432947533094</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8703396507439852</v>
+        <v>0.9664325936078386</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05366359745808709</v>
+        <v>0.0001533848665085649</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>279</v>
+        <v>406</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9394355448277806</v>
+        <v>0.8102458164270864</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -618,37 +618,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5217809286535533</v>
+        <v>0.5217838084711208</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>46052.30529379629</v>
+        <v>46053.03943832176</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>46052.3060081713</v>
+        <v>46053.04012222222</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.0007143746990740741</v>
+        <v>0.0006838929398148148</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9976061155707107</v>
+        <v>0.9687816959411472</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7303601552311965</v>
+        <v>0.9070101399146729</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02115027889701121</v>
+        <v>0.008572354768589698</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>475</v>
+        <v>202</v>
       </c>
       <c r="K5" t="n">
-        <v>0.888673687817483</v>
+        <v>0.9478191656086956</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -658,37 +658,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5217860227390329</v>
+        <v>0.5217841543796622</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>46052.29711053241</v>
+        <v>46053.03707181713</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>46052.29779002315</v>
+        <v>46053.03765398148</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.0006795019907407407</v>
+        <v>0.0005821625925925926</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9652383327425097</v>
+        <v>0.9339268149824255</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7612597965280045</v>
+        <v>0.959516265739795</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003887046234237243</v>
+        <v>9.246270681332712e-05</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>408</v>
+        <v>215</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9104825940173162</v>
+        <v>0.8446353208822238</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -698,37 +698,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5217926691204967</v>
+        <v>0.5217869201228497</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>46052.29903483796</v>
+        <v>46053.02869336805</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>46052.29971357639</v>
+        <v>46053.02926405093</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.0006787412384259259</v>
+        <v>0.0005706806828703704</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9993918741325356</v>
+        <v>0.8626316357484652</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6740821605973291</v>
+        <v>0.9548756303988334</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007401748257392407</v>
+        <v>0.002858683303275054</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>479</v>
+        <v>151</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7994796293235455</v>
+        <v>0.7191567383285878</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -738,37 +738,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5217958235215046</v>
+        <v>0.5217902497087119</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>46052.29644137732</v>
+        <v>46053.0318640625</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>46052.29711052083</v>
+        <v>46053.0324615162</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.0006691427893518519</v>
+        <v>0.0005974584953703703</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9751574253005152</v>
+        <v>0.9339298636568966</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8122719575376807</v>
+        <v>0.9577761697385455</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03033680787342682</v>
+        <v>9.85914332834297e-05</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>469</v>
+        <v>216</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9226587148787183</v>
+        <v>0.8408658702632296</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -778,37 +778,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5217996259057637</v>
+        <v>0.5217927004704552</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>46052.29971358796</v>
+        <v>46053.03765399306</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>46052.30036280092</v>
+        <v>46053.03824574074</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.0006492126851851852</v>
+        <v>0.0005917528587962963</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9311923017541734</v>
+        <v>0.9166436820590279</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6867262054219923</v>
+        <v>0.9671193047469436</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01198097695505565</v>
+        <v>3.525259983125323e-05</v>
       </c>
       <c r="I9" t="n">
         <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>206</v>
+        <v>297</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8021907471822373</v>
+        <v>0.8542676165695934</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -818,37 +818,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5218011602506815</v>
+        <v>0.5217941510170319</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>46052.30168855324</v>
+        <v>46053.0276520949</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>46052.30236142361</v>
+        <v>46053.02821614583</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.0006728721759259259</v>
+        <v>0.0005640585069444444</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8942968414902877</v>
+        <v>0.8638902493993836</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6891894495986435</v>
+        <v>0.8968052567533491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0003552459736251283</v>
+        <v>0.0002811554484412652</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>279</v>
+        <v>163</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8758107981320498</v>
+        <v>0.7941918863008114</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -858,37 +858,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5218023155008424</v>
+        <v>0.5217952776744739</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>46052.27824193287</v>
+        <v>46053.02660103009</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>46052.2789271875</v>
+        <v>46053.02716369213</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.000685263275462963</v>
+        <v>0.0005626574074074073</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8006591385428447</v>
+        <v>0.899857204058397</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7990863390699525</v>
+        <v>0.9761545347722832</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001074952157404828</v>
+        <v>0.0002622415652954746</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>197</v>
+        <v>497</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9671453176972686</v>
+        <v>0.7927433547815091</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -898,37 +898,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5218060304141811</v>
+        <v>0.5217957791884001</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>46052.28909482639</v>
+        <v>46053.04197247685</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>46052.28975935185</v>
+        <v>46053.04260855324</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.0006645182870370371</v>
+        <v>0.0006360791435185185</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9911200475858406</v>
+        <v>0.9178615691364596</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8547167585886166</v>
+        <v>0.9009389577616517</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05488883113825946</v>
+        <v>8.148058512546357e-05</v>
       </c>
       <c r="I12" t="n">
         <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9348952594555011</v>
+        <v>0.850031245895539</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -938,37 +938,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5218061968320404</v>
+        <v>0.5217962375260583</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>46052.3060081713</v>
+        <v>46053.04070151621</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>46052.30663942129</v>
+        <v>46053.04134758102</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.0006312493518518519</v>
+        <v>0.0006460690277777778</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9560856439802604</v>
+        <v>0.9395388824858462</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7313295273477936</v>
+        <v>0.9143743135728249</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01809869847872205</v>
+        <v>3.484511597391089e-06</v>
       </c>
       <c r="I13" t="n">
         <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>350</v>
+        <v>399</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8995683122839064</v>
+        <v>0.9581148082102414</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -978,37 +978,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5218077858139808</v>
+        <v>0.5218000642078093</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>46052.29101657408</v>
+        <v>46053.02475097222</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>46052.29165434028</v>
+        <v>46053.0253909838</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.0006377657407407408</v>
+        <v>0.0006400131712962963</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9191175594478779</v>
+        <v>0.9969567700011791</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8629165604956325</v>
+        <v>0.9954490862711169</v>
       </c>
       <c r="H14" t="n">
-        <v>0.02843052679483453</v>
+        <v>0.0001149875937105774</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>20</v>
+        <v>827</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9424048142670677</v>
+        <v>0.889416161477478</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1021,34 +1021,34 @@
         <v>43</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5218078185797524</v>
+        <v>0.5218065871387775</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>46052.30457018519</v>
+        <v>46053.03824575232</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>46052.30529378472</v>
+        <v>46053.03881765046</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.0007235953935185185</v>
+        <v>0.0005718904166666667</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9343964962973308</v>
+        <v>0.9999197063794087</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7035433032596216</v>
+        <v>0.9306603900454521</v>
       </c>
       <c r="H15" t="n">
-        <v>0.002827597854487416</v>
+        <v>6.084528888575307e-05</v>
       </c>
       <c r="I15" t="n">
         <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9833807379234946</v>
+        <v>0.8840911348945384</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1058,37 +1058,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="B16" t="n">
-        <v>0.5218087126279166</v>
+        <v>0.5218069905482575</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>46052.28514100694</v>
+        <v>46053.03881765046</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>46052.28581571759</v>
+        <v>46053.03943832176</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.0006747154398148149</v>
+        <v>0.0006206629166666666</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8612987615562508</v>
+        <v>0.9510960172349503</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9164290620623823</v>
+        <v>0.8669244446927356</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1495165544973579</v>
+        <v>0.0004763376709462822</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>195</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9274915566056072</v>
+        <v>0.8088146229289568</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1098,37 +1098,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B17" t="n">
-        <v>0.5218093865713801</v>
+        <v>0.5218079194042409</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>46052.30862040509</v>
+        <v>46053.03378865741</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>46052.30939314815</v>
+        <v>46053.03436914352</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.0007727339699074074</v>
+        <v>0.0005804875231481481</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5542988570882174</v>
+        <v>0.9271950763633061</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8874008594316017</v>
+        <v>0.9274307690661133</v>
       </c>
       <c r="H17" t="n">
-        <v>0.09944807483919607</v>
+        <v>1.107602380537716e-06</v>
       </c>
       <c r="I17" t="n">
         <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>248</v>
+        <v>521</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8517873344575452</v>
+        <v>0.8287867406775197</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1138,37 +1138,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5218138255543077</v>
+        <v>0.5218111439244972</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>46052.28975935185</v>
+        <v>46053.03489659722</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>46052.2903349537</v>
+        <v>46053.03557371528</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.0005755960416666667</v>
+        <v>0.0006771220833333333</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9933596469689429</v>
+        <v>0.9118615838020094</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8344886237577736</v>
+        <v>0.8508744265586126</v>
       </c>
       <c r="H18" t="n">
-        <v>0.000623210592599581</v>
+        <v>1.351050816235072e-05</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8440707037425368</v>
+        <v>0.9577284272478734</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1178,37 +1178,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B19" t="n">
-        <v>0.521814390292341</v>
+        <v>0.5218138966742237</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>46052.283894375</v>
+        <v>46053.03314049768</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>46052.28453164352</v>
+        <v>46053.03378864584</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.0006372752546296296</v>
+        <v>0.0006481486342592592</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8757606865238299</v>
+        <v>0.9495357126852143</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9809035869575056</v>
+        <v>0.8457356261937086</v>
       </c>
       <c r="H19" t="n">
-        <v>0.003460110971128931</v>
+        <v>1.700544311200966e-05</v>
       </c>
       <c r="I19" t="n">
         <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9702800193922332</v>
+        <v>0.912541602990676</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1218,37 +1218,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B20" t="n">
-        <v>0.5218149805655476</v>
+        <v>0.5218143728946496</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>46052.30379466435</v>
+        <v>46053.0413475926</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>46052.30457017361</v>
+        <v>46053.04197246527</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.0007755129861111112</v>
+        <v>0.000624878761574074</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9705617703785266</v>
+        <v>0.9793798626317357</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7563329542117924</v>
+        <v>0.7292626180801829</v>
       </c>
       <c r="H20" t="n">
-        <v>0.009991123995985009</v>
+        <v>0.0653199103115274</v>
       </c>
       <c r="I20" t="n">
         <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>884</v>
+        <v>229</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9587407367374674</v>
+        <v>0.9133054448056555</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1258,37 +1258,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.5218197288986147</v>
+        <v>0.5218163043415129</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>46052.29284724537</v>
+        <v>46053.02539099537</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>46052.29349016204</v>
+        <v>46053.02599424768</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.0006429195833333333</v>
+        <v>0.0006032565625</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8195500544891801</v>
+        <v>0.9876223594793404</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8205573828411855</v>
+        <v>0.996297728811439</v>
       </c>
       <c r="H21" t="n">
-        <v>0.02386408782674527</v>
+        <v>8.201151850992443e-06</v>
       </c>
       <c r="I21" t="n">
         <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>257</v>
+        <v>878</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9455308907358494</v>
+        <v>0.8636602553934588</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1298,37 +1298,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="n">
-        <v>0.5218214716828017</v>
+        <v>0.5218185884788384</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>46052.2845316551</v>
+        <v>46053.01811709491</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>46052.28514099537</v>
+        <v>46053.01903586806</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.0006093390277777778</v>
+        <v>0.0009187659722222221</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8580051402888705</v>
+        <v>0.5081256231292735</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8904153146535987</v>
+        <v>0.6682812823335732</v>
       </c>
       <c r="H22" t="n">
-        <v>0.006192487532616074</v>
+        <v>6.207919263907712e-05</v>
       </c>
       <c r="I22" t="n">
         <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>141</v>
+        <v>17</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9697122080138758</v>
+        <v>0.9935341349679258</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1338,37 +1338,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B23" t="n">
-        <v>0.5218220509286378</v>
+        <v>0.5218235488588121</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>46052.30663943287</v>
+        <v>46053.0343691551</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>46052.30727077546</v>
+        <v>46053.03489658565</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.0006313432291666667</v>
+        <v>0.0005274278935185185</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7723934208738518</v>
+        <v>0.9645657402777699</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7737421252443596</v>
+        <v>0.9717586842908</v>
       </c>
       <c r="H23" t="n">
-        <v>2.794746388491205e-05</v>
+        <v>5.450228441950504e-06</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>142</v>
+        <v>260</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8888598705489528</v>
+        <v>0.6555391464701876</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1378,37 +1378,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B24" t="n">
-        <v>0.5218245124910137</v>
+        <v>0.5218271444376549</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>46052.29779003473</v>
+        <v>46053.03078534722</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>46052.29844833333</v>
+        <v>46053.03129449074</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.0006583014120370371</v>
+        <v>0.0005091390856481482</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9586436583028994</v>
+        <v>0.8722134359675821</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7366723686329181</v>
+        <v>0.9091506663959446</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0003739143179427847</v>
+        <v>0.001542154864558084</v>
       </c>
       <c r="I24" t="n">
         <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>662</v>
+        <v>215</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9123207032461526</v>
+        <v>0.7403235748510245</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1418,37 +1418,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.5218255517491086</v>
+        <v>0.5218338093515683</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>46052.27892719908</v>
+        <v>46053.0271637037</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>46052.27947258102</v>
+        <v>46053.02765208334</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.0005453856481481481</v>
+        <v>0.0004883818865740741</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7134748438459986</v>
+        <v>0.9079693319046106</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9950367545830106</v>
+        <v>0.939936969421879</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0005798287364073807</v>
+        <v>0.000157463329003125</v>
       </c>
       <c r="I25" t="n">
         <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>158</v>
+        <v>412</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8290033660459908</v>
+        <v>0.7598971041413385</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1458,37 +1458,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B26" t="n">
-        <v>0.5218282106115616</v>
+        <v>0.5218338771497477</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>46052.29844834491</v>
+        <v>46053.04012222222</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>46052.29903482639</v>
+        <v>46053.04070150463</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.0005864834953703703</v>
+        <v>0.0005792742939814815</v>
       </c>
       <c r="F26" t="n">
-        <v>0.902693006522975</v>
+        <v>0.9673996434655765</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7549724392570567</v>
+        <v>0.9993507863823154</v>
       </c>
       <c r="H26" t="n">
-        <v>0.002073457558068545</v>
+        <v>0.01606066450913643</v>
       </c>
       <c r="I26" t="n">
         <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>452</v>
+        <v>615</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8577182714118197</v>
+        <v>0.9307378443126968</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1498,37 +1498,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B27" t="n">
-        <v>0.5218290792217843</v>
+        <v>0.5218349254438718</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>46052.29227322917</v>
+        <v>46053.0136635301</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>46052.2928472338</v>
+        <v>46053.01432476852</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.0005740079513888889</v>
+        <v>0.0006612372337962963</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8869443142219485</v>
+        <v>0.9600164932892497</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9445574795028227</v>
+        <v>0.7625585681679015</v>
       </c>
       <c r="H27" t="n">
-        <v>0.06014481005629807</v>
+        <v>0.07738296284945649</v>
       </c>
       <c r="I27" t="n">
         <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>25</v>
+        <v>227</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8745121901295738</v>
+        <v>0.9544699506529921</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1538,37 +1538,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B28" t="n">
-        <v>0.5218360570972029</v>
+        <v>0.5218359267133053</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>46052.29560778935</v>
+        <v>46053.02821615741</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>46052.29644136574</v>
+        <v>46053.02869335648</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.0008335746412037036</v>
+        <v>0.0004772005555555556</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6630372641176105</v>
+        <v>0.8360140667037811</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7174986671394382</v>
+        <v>0.8916659675210497</v>
       </c>
       <c r="H28" t="n">
-        <v>0.004376244533980977</v>
+        <v>0.0004535704116304097</v>
       </c>
       <c r="I28" t="n">
         <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>676</v>
+        <v>146</v>
       </c>
       <c r="K28" t="n">
-        <v>0.9617327139619404</v>
+        <v>0.8010213303586892</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1578,37 +1578,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B29" t="n">
-        <v>0.5218394575219001</v>
+        <v>0.5218379108455137</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>46052.29349017361</v>
+        <v>46053.02599425926</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>46052.29408069445</v>
+        <v>46053.02660101852</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.000590519525462963</v>
+        <v>0.0006067633564814815</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9438490021155118</v>
+        <v>0.9821852249211696</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8689432506897701</v>
+        <v>0.9885417341623373</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1972690417767676</v>
+        <v>8.31352226548217e-06</v>
       </c>
       <c r="I29" t="n">
         <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>36</v>
+        <v>975</v>
       </c>
       <c r="K29" t="n">
-        <v>0.8738407086410238</v>
+        <v>0.8693504333400864</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1618,37 +1618,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B30" t="n">
-        <v>0.5218495422153046</v>
+        <v>0.5218389170773311</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>46052.29172631945</v>
+        <v>46053.01243510417</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>46052.29227321759</v>
+        <v>46053.01308200231</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.0005468990162037036</v>
+        <v>0.0006468987152777778</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9230205710373284</v>
+        <v>0.7680163437728287</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7514435242322495</v>
+        <v>0.6816655735538059</v>
       </c>
       <c r="H30" t="n">
-        <v>0.001767517426257633</v>
+        <v>0.000319875555320078</v>
       </c>
       <c r="I30" t="n">
         <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>362</v>
+        <v>8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7962109825651373</v>
+        <v>0.9409342633711633</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1658,37 +1658,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="B31" t="n">
-        <v>0.52185411690187</v>
+        <v>0.521839576325505</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>46052.30727078704</v>
+        <v>46053.01599290509</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>46052.30804537037</v>
+        <v>46053.01658210648</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.000774585798611111</v>
+        <v>0.0005892028819444444</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9737601665726169</v>
+        <v>0.7466073791322096</v>
       </c>
       <c r="G31" t="n">
-        <v>0.791561052099677</v>
+        <v>0.9181166212335455</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1186654879399005</v>
+        <v>0.02515444994841259</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9481904976624411</v>
+        <v>0.929141916124579</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -1698,37 +1698,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B32" t="n">
-        <v>0.5218617005268923</v>
+        <v>0.521847067203187</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>46052.28712744213</v>
+        <v>46053.01106219908</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>46052.28796966435</v>
+        <v>46053.01154927084</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0.0008422218171296297</v>
+        <v>0.0004870745717592593</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9100993220821891</v>
+        <v>0.9379248806070901</v>
       </c>
       <c r="G32" t="n">
-        <v>0.650624501287933</v>
+        <v>0.8356067725124527</v>
       </c>
       <c r="H32" t="n">
-        <v>0.06644968859961414</v>
+        <v>0.0003439423395166844</v>
       </c>
       <c r="I32" t="n">
         <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K32" t="n">
-        <v>0.9070297319856988</v>
+        <v>0.63271701233956</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -1738,37 +1738,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B33" t="n">
-        <v>0.5218771904101005</v>
+        <v>0.5218494135612403</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>46052.28088577546</v>
+        <v>46053.03021092593</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>46052.28146065972</v>
+        <v>46053.03078533565</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.0005748909606481482</v>
+        <v>0.0005744093981481481</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7903307902033583</v>
+        <v>0.9368625536697763</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8208950995526447</v>
+        <v>0.829762389367949</v>
       </c>
       <c r="H33" t="n">
-        <v>5.527673564096294e-06</v>
+        <v>0.0006395370163978473</v>
       </c>
       <c r="I33" t="n">
         <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6114538945354608</v>
+        <v>0.7024762192562801</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -1778,37 +1778,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>0.5218802265595317</v>
+        <v>0.5218518162774368</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>46052.28269303241</v>
+        <v>46053.03607618056</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>46052.28319344908</v>
+        <v>46053.03657603009</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.0005004188310185185</v>
+        <v>0.0004998535648148148</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7614442133134555</v>
+        <v>0.9612967297787581</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9758235341740962</v>
+        <v>0.9628745939286552</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01389538774193144</v>
+        <v>0.0007404001486285348</v>
       </c>
       <c r="I34" t="n">
         <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>624</v>
+        <v>538</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6689416544705935</v>
+        <v>0.7777867792583789</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -1818,37 +1818,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B35" t="n">
-        <v>0.5218805661698834</v>
+        <v>0.5218602103201776</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>46052.2884071875</v>
+        <v>46053.01308201389</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>46052.28909481481</v>
+        <v>46053.01366351852</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0.0006876351041666666</v>
+        <v>0.000581505613425926</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6557077821820855</v>
+        <v>0.9723231378726116</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7880135674559801</v>
+        <v>0.8312220082482233</v>
       </c>
       <c r="H35" t="n">
-        <v>0.001423623448984785</v>
+        <v>4.012886024880091e-06</v>
       </c>
       <c r="I35" t="n">
         <v>2</v>
       </c>
       <c r="J35" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>0.7546974133545002</v>
+        <v>0.8049545452140272</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -1858,37 +1858,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>0.5218894044995895</v>
+        <v>0.5218633087364571</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>46052.28581572917</v>
+        <v>46053.03657604167</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>46052.28663702546</v>
+        <v>46053.03707180556</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.0008212924652777778</v>
+        <v>0.0004957695949074075</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8297851574441182</v>
+        <v>0.8837052851772529</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7835185198250264</v>
+        <v>0.9192840869542453</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2643619924789058</v>
+        <v>0.0001947110218607746</v>
       </c>
       <c r="I36" t="n">
         <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>291</v>
+        <v>112</v>
       </c>
       <c r="K36" t="n">
-        <v>0.9029214930152754</v>
+        <v>0.8202356635777229</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -1898,37 +1898,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B37" t="n">
-        <v>0.5218915597159358</v>
+        <v>0.521863371208231</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>46052.28663702546</v>
+        <v>46053.0292640625</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>46052.28712744213</v>
+        <v>46053.02971898148</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.0004904070138888889</v>
+        <v>0.0004549181712962963</v>
       </c>
       <c r="F37" t="n">
-        <v>0.605823674981362</v>
+        <v>0.8537909574850485</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9053434668397299</v>
+        <v>0.8783679202334559</v>
       </c>
       <c r="H37" t="n">
-        <v>1.144683363560707e-06</v>
+        <v>0.002761196559993196</v>
       </c>
       <c r="I37" t="n">
         <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7664763184385768</v>
+        <v>0.5643258230808715</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -1938,37 +1938,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B38" t="n">
-        <v>0.5219084509169634</v>
+        <v>0.5218703204825914</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>46052.28319346065</v>
+        <v>46053.02971899306</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>46052.28385864583</v>
+        <v>46053.03021091435</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.0006651867592592592</v>
+        <v>0.0004919289351851851</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7381735918636688</v>
+        <v>0.7987328054136515</v>
       </c>
       <c r="G38" t="n">
-        <v>0.6714801940137189</v>
+        <v>0.9460961336537081</v>
       </c>
       <c r="H38" t="n">
-        <v>4.781798743420834e-05</v>
+        <v>0.005323322365207566</v>
       </c>
       <c r="I38" t="n">
         <v>2</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="K38" t="n">
-        <v>0.8420957660586726</v>
+        <v>0.7111810902989145</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -1978,37 +1978,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B39" t="n">
-        <v>0.5219143303711882</v>
+        <v>0.5218710769844203</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>46052.28146067129</v>
+        <v>46053.02217550926</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>46052.28210159722</v>
+        <v>46053.02280160879</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0.0006409253587962963</v>
+        <v>0.0006261023148148148</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7048829642363457</v>
+        <v>0.5784276707981424</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7179979466813797</v>
+        <v>0.8742426307216145</v>
       </c>
       <c r="H39" t="n">
-        <v>0.000159585519881693</v>
+        <v>5.490998593240598e-05</v>
       </c>
       <c r="I39" t="n">
         <v>2</v>
       </c>
       <c r="J39" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="K39" t="n">
-        <v>0.8895525943066782</v>
+        <v>0.7719720046453322</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2018,37 +2018,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B40" t="n">
-        <v>0.52191823359959</v>
+        <v>0.5218810456053783</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>46052.28796967593</v>
+        <v>46053.0115492824</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>46052.28840717593</v>
+        <v>46053.01243510417</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.0004374982523148149</v>
+        <v>0.0008858183912037038</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7968392357900305</v>
+        <v>0.8931159755876732</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9232142610613518</v>
+        <v>0.6409457581764266</v>
       </c>
       <c r="H40" t="n">
-        <v>0.07010236138503083</v>
+        <v>0.001499878130537944</v>
       </c>
       <c r="I40" t="n">
         <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>407</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
-        <v>0.5260355144104041</v>
+        <v>0.9530123275298035</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2058,37 +2058,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="B41" t="n">
-        <v>0.5219232671691237</v>
+        <v>0.5218823557512871</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>46052.30236143518</v>
+        <v>46053.01658211806</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>46052.30309206019</v>
+        <v>46053.01716159722</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.0007306307523148148</v>
+        <v>0.0005794742708333334</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9677899583502357</v>
+        <v>0.7725075124677702</v>
       </c>
       <c r="G41" t="n">
-        <v>0.5452755278419125</v>
+        <v>0.787695340061922</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00589472313905191</v>
+        <v>0.001053154446149926</v>
       </c>
       <c r="I41" t="n">
         <v>2</v>
       </c>
       <c r="J41" t="n">
-        <v>626</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>0.6554128933420333</v>
+        <v>0.6685715799838094</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2098,37 +2098,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B42" t="n">
-        <v>0.5219484176342351</v>
+        <v>0.5218899060138462</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>46052.27755006945</v>
+        <v>46053.03557372685</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>46052.2782419213</v>
+        <v>46053.03607616898</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>0.0006918477777777777</v>
+        <v>0.0005024385185185185</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6843880211569958</v>
+        <v>0.8764351918383968</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5042396814782091</v>
+        <v>0.80657415990242</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0001273755143519654</v>
+        <v>0.001890850701225007</v>
       </c>
       <c r="I42" t="n">
         <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>325</v>
       </c>
       <c r="K42" t="n">
-        <v>0.8280964707788323</v>
+        <v>0.7351707033656069</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2138,37 +2138,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="B43" t="n">
-        <v>0.521949368040236</v>
+        <v>0.5219324159844196</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>46052.30099601852</v>
+        <v>46053.01492773148</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>46052.30168854167</v>
+        <v>46053.01550195602</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.0006925283217592592</v>
+        <v>0.0005742300347222223</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9466252827087279</v>
+        <v>0.661775973292842</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5948106471197594</v>
+        <v>0.7572051291978743</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0008376296556669569</v>
+        <v>0.01010639441521232</v>
       </c>
       <c r="I43" t="n">
         <v>2</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>331</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8185250395166428</v>
+        <v>0.5040037622325447</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2178,37 +2178,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B44" t="n">
-        <v>0.5219576604401663</v>
+        <v>0.5219441285042465</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>46052.29484628472</v>
+        <v>46053.02353143519</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>46052.29560777778</v>
+        <v>46053.02411988426</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0.000761502962962963</v>
+        <v>0.0005884520486111112</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8412980836340701</v>
+        <v>0.7037968016316116</v>
       </c>
       <c r="G44" t="n">
-        <v>0.6293684317241576</v>
+        <v>0.7675300226268523</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0001942438597539642</v>
+        <v>0.004251139140083427</v>
       </c>
       <c r="I44" t="n">
         <v>2</v>
       </c>
       <c r="J44" t="n">
-        <v>982</v>
+        <v>10</v>
       </c>
       <c r="K44" t="n">
-        <v>0.7967239491866115</v>
+        <v>0.7090087334169517</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2218,37 +2218,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="B45" t="n">
-        <v>0.521966661105324</v>
+        <v>0.5219747086012192</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>46052.30804538194</v>
+        <v>46053.0143247801</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>46052.30862040509</v>
+        <v>46053.01492771991</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.0005750195138888889</v>
+        <v>0.0006029416435185185</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8802562628675538</v>
+        <v>0.900381759104174</v>
       </c>
       <c r="G45" t="n">
-        <v>0.8323208571325125</v>
+        <v>0.630270236605696</v>
       </c>
       <c r="H45" t="n">
-        <v>0.03766919560639086</v>
+        <v>0.0195831787718444</v>
       </c>
       <c r="I45" t="n">
         <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>989</v>
+        <v>341</v>
       </c>
       <c r="K45" t="n">
-        <v>0.980629637806214</v>
+        <v>0.6140094562377012</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2258,37 +2258,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B46" t="n">
-        <v>0.521969181957782</v>
+        <v>0.5219768376119408</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>46052.3003628125</v>
+        <v>46053.0171616088</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>46052.30099600695</v>
+        <v>46053.01811708333</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.0006331923842592593</v>
+        <v>0.0009554820254629629</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9980556025106548</v>
+        <v>0.8283500406505555</v>
       </c>
       <c r="G46" t="n">
-        <v>0.6087653164726698</v>
+        <v>0.5382869773972454</v>
       </c>
       <c r="H46" t="n">
-        <v>5.599258781080313e-05</v>
+        <v>0.3038768518489103</v>
       </c>
       <c r="I46" t="n">
         <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>104</v>
+        <v>693</v>
       </c>
       <c r="K46" t="n">
-        <v>0.7190078591936142</v>
+        <v>0.8307089957103893</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2298,37 +2298,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B47" t="n">
-        <v>0.521970328951882</v>
+        <v>0.5219856492575287</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>46052.27947259259</v>
+        <v>46053.01550196759</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>46052.28002649306</v>
+        <v>46053.01599289352</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.0005538976388888889</v>
+        <v>0.0004909267476851852</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5157168482328258</v>
+        <v>0.5630499192528069</v>
       </c>
       <c r="G47" t="n">
-        <v>0.7123357496134081</v>
+        <v>0.7190896913969682</v>
       </c>
       <c r="H47" t="n">
-        <v>5.929117799347046e-05</v>
+        <v>2.291551230328529e-06</v>
       </c>
       <c r="I47" t="n">
         <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5811925379264831</v>
+        <v>0.507423056671289</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2338,37 +2338,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B48" t="n">
-        <v>0.5220217636083979</v>
+        <v>0.5220849560458395</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>46052.2821016088</v>
+        <v>46053.01903586806</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>46052.28269302083</v>
+        <v>46053.02014494213</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.0005914156481481482</v>
+        <v>0.001109072638888889</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9515104083911288</v>
+        <v>0.5092398291810144</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5594166860286126</v>
+        <v>0.5502514150230507</v>
       </c>
       <c r="H48" t="n">
-        <v>1.488649800689049e-05</v>
+        <v>2.611817201564411e-05</v>
       </c>
       <c r="I48" t="n">
         <v>2</v>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K48" t="n">
-        <v>0.6877549723855942</v>
+        <v>0.9895319210124913</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2378,37 +2378,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B49" t="n">
-        <v>0.522212827190649</v>
+        <v>0.5220929697797813</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>46052.28002650463</v>
+        <v>46053.02110571759</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>46052.28088576389</v>
+        <v>46053.02217549769</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>0.0008592618634259259</v>
+        <v>0.001069778136574074</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5298741506025164</v>
+        <v>0.651196859908229</v>
       </c>
       <c r="G49" t="n">
-        <v>0.5111667884145589</v>
+        <v>0.588357967161067</v>
       </c>
       <c r="H49" t="n">
-        <v>0.01134415996038949</v>
+        <v>3.275738995849058e-05</v>
       </c>
       <c r="I49" t="n">
         <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>891</v>
+        <v>25</v>
       </c>
       <c r="K49" t="n">
-        <v>0.6976177009326144</v>
+        <v>0.8981521102680734</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2418,37 +2418,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B50" t="n">
-        <v>0.5258649078337927</v>
+        <v>0.522148713668759</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>46052.29165434028</v>
+        <v>46053.02014495371</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>46052.29172630787</v>
+        <v>46053.02110570602</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>7.196148148148149e-05</v>
+        <v>0.0009607530555555554</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9896726976644845</v>
+        <v>0.6451188485710126</v>
       </c>
       <c r="G50" t="n">
-        <v>0.779734292032889</v>
+        <v>0.9468511490415169</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5141762134702791</v>
+        <v>0.5270914924390533</v>
       </c>
       <c r="I50" t="n">
         <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="K50" t="n">
-        <v>0.9937821121092973</v>
+        <v>0.861218701370966</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2458,37 +2458,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B51" t="n">
-        <v>0.5260948522893641</v>
+        <v>0.5225447450019673</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>46052.28385865741</v>
+        <v>46053.02280162037</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>46052.28389436343</v>
+        <v>46053.02353142361</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>3.570594907407408e-05</v>
+        <v>0.0007298101620370371</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9629785064427886</v>
+        <v>0.8244002703245845</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8547795312117996</v>
+        <v>0.6908606706302014</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8080519187513185</v>
+        <v>0.07143187820212153</v>
       </c>
       <c r="I51" t="n">
         <v>2</v>
       </c>
       <c r="J51" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>0.9991398504843021</v>
+        <v>0.9975882023326321</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11949.68721711187</v>
+        <v>11251.4796097378</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2335019908024273</v>
+        <v>0.2331961793255745</v>
       </c>
     </row>
     <row r="3">
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11053.3556764414</v>
+        <v>10105.473340219</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2159872897593864</v>
+        <v>0.2094442557737914</v>
       </c>
     </row>
     <row r="4">
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7087.7144950552</v>
+        <v>7049.82687947191</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1384969677252027</v>
+        <v>0.1461134668703273</v>
       </c>
     </row>
     <row r="5">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4406.4859210867</v>
+        <v>4133.270171279</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08610461649098236</v>
+        <v>0.08566542761437643</v>
       </c>
     </row>
     <row r="6">
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4387.1523717945</v>
+        <v>4001.450463562</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0857268306822843</v>
+        <v>0.08293335563223338</v>
       </c>
     </row>
     <row r="7">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2716.2558133229</v>
+        <v>2620.661371042</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05307679844802298</v>
+        <v>0.05431536475471226</v>
       </c>
     </row>
     <row r="8">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2578.30057427878</v>
+        <v>2332.87486518643</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05038109416947934</v>
+        <v>0.04835075245884196</v>
       </c>
     </row>
     <row r="9">
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1875.5511647679</v>
+        <v>1945.5167532018</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03664907062989747</v>
+        <v>0.04032243663916918</v>
       </c>
     </row>
     <row r="10">
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1399.6104495277</v>
+        <v>1265.465038819</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02734898582488467</v>
+        <v>0.02622780490730121</v>
       </c>
     </row>
     <row r="11">
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1331.4221096865</v>
+        <v>1247.4864379309</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02601655654760348</v>
+        <v>0.02585518360040254</v>
       </c>
     </row>
     <row r="12">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>846.8643967809001</v>
+        <v>825.824257711</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01654809192870488</v>
+        <v>0.01711588772075032</v>
       </c>
     </row>
     <row r="13">
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>680.2080919637</v>
+        <v>688.1238389169999</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01329155656944736</v>
+        <v>0.01426193315938746</v>
       </c>
     </row>
     <row r="14">
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>678.567248353</v>
+        <v>628.292242119</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01325949378464533</v>
+        <v>0.0130218740507022</v>
       </c>
     </row>
     <row r="15">
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94.9345947897</v>
+        <v>78.442019645</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001855062519768141</v>
+        <v>0.00162577544592128</v>
       </c>
     </row>
     <row r="16">
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>89.8442043659</v>
+        <v>74.800504518</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001755594117263277</v>
+        <v>0.001550302046508305</v>
       </c>
     </row>
   </sheetData>
